--- a/DSA_REV.xlsx
+++ b/DSA_REV.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="100">
   <si>
     <t>problem</t>
   </si>
@@ -314,9 +314,6 @@
     <t>692. Top K Frequent Words</t>
   </si>
   <si>
-    <t xml:space="preserve"> </t>
-  </si>
-  <si>
     <t>105. Construct Binary Tree from Preorder and Inorder Traversal</t>
   </si>
   <si>
@@ -351,6 +348,18 @@
   </si>
   <si>
     <t>3may</t>
+  </si>
+  <si>
+    <t>547. Number of Provinces</t>
+  </si>
+  <si>
+    <t>5may</t>
+  </si>
+  <si>
+    <t>994. Rotting Oranges</t>
+  </si>
+  <si>
+    <t>11may</t>
   </si>
 </sst>
 </file>
@@ -571,12 +580,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="Times New Roman"/>
       <charset val="0"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="Times New Roman"/>
       <charset val="0"/>
@@ -1139,19 +1148,19 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1687,7 +1696,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AF42"/>
+  <dimension ref="A1:AG44"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="8.81818181818182"/>
@@ -2030,7 +2039,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" ht="182" spans="1:32">
+    <row r="17" ht="182" spans="1:33">
       <c r="A17" s="13" t="s">
         <v>35</v>
       </c>
@@ -2055,7 +2064,7 @@
       </c>
       <c r="X17" s="15"/>
     </row>
-    <row r="18" ht="26" spans="1:32">
+    <row r="18" ht="26" spans="1:33">
       <c r="A18" s="4" t="s">
         <v>39</v>
       </c>
@@ -2097,7 +2106,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="19" ht="26" spans="1:32">
+    <row r="19" ht="26" spans="1:33">
       <c r="A19" s="8">
         <v>1390</v>
       </c>
@@ -2127,7 +2136,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="20" spans="1:32">
+    <row r="20" spans="1:33">
       <c r="A20" s="1" t="s">
         <v>46</v>
       </c>
@@ -2149,7 +2158,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:32">
+    <row r="21" spans="1:33">
       <c r="A21" s="13" t="s">
         <v>48</v>
       </c>
@@ -2171,7 +2180,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" ht="26" spans="1:32">
+    <row r="22" ht="26" spans="1:33">
       <c r="A22" s="8" t="s">
         <v>50</v>
       </c>
@@ -2199,7 +2208,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="23" ht="182" spans="1:32">
+    <row r="23" ht="182" spans="1:33">
       <c r="A23" s="1" t="s">
         <v>52</v>
       </c>
@@ -2220,7 +2229,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="24" ht="208" spans="1:32">
+    <row r="24" ht="208" spans="1:33">
       <c r="A24" s="9" t="s">
         <v>55</v>
       </c>
@@ -2237,7 +2246,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="25" ht="156" spans="1:32">
+    <row r="25" ht="156" spans="1:33">
       <c r="A25" s="9" t="s">
         <v>57</v>
       </c>
@@ -2261,7 +2270,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="26" ht="182" spans="1:32">
+    <row r="26" ht="182" spans="1:33">
       <c r="A26" s="25" t="s">
         <v>59</v>
       </c>
@@ -2284,7 +2293,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="27" ht="78" spans="1:32">
+    <row r="27" ht="78" spans="1:33">
       <c r="A27" s="25" t="s">
         <v>63</v>
       </c>
@@ -2305,7 +2314,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="28" spans="1:32">
+    <row r="28" spans="1:33">
       <c r="A28" s="1" t="s">
         <v>65</v>
       </c>
@@ -2322,21 +2331,34 @@
         <v>46083</v>
       </c>
     </row>
-    <row r="29" ht="26" spans="1:32">
+    <row r="29" ht="26" spans="1:33">
       <c r="A29" s="16" t="s">
         <v>68</v>
       </c>
       <c r="D29" s="10">
         <v>46068</v>
       </c>
-      <c r="U29" s="16" t="s">
+      <c r="U29" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="AF29" s="10">
+      <c r="V29" s="1"/>
+      <c r="W29" s="1"/>
+      <c r="X29" s="1"/>
+      <c r="Y29" s="1"/>
+      <c r="Z29" s="1"/>
+      <c r="AA29" s="1"/>
+      <c r="AB29" s="1"/>
+      <c r="AC29" s="1"/>
+      <c r="AD29" s="1"/>
+      <c r="AE29" s="1"/>
+      <c r="AF29" s="2">
         <v>46082</v>
       </c>
-    </row>
-    <row r="30" ht="26" spans="1:32">
+      <c r="AG29" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" ht="26" spans="1:33">
       <c r="A30" s="8" t="s">
         <v>70</v>
       </c>
@@ -2353,16 +2375,25 @@
       <c r="U30" s="26" t="s">
         <v>72</v>
       </c>
-      <c r="AB30" s="10">
+      <c r="V30" s="1"/>
+      <c r="W30" s="1"/>
+      <c r="X30" s="1"/>
+      <c r="Y30" s="1"/>
+      <c r="Z30" s="1"/>
+      <c r="AA30" s="1"/>
+      <c r="AB30" s="2">
         <v>46087</v>
       </c>
     </row>
-    <row r="31" ht="208" spans="1:32">
-      <c r="A31" s="27" t="s">
+    <row r="31" ht="208" spans="1:33">
+      <c r="A31" s="24" t="s">
         <v>73</v>
       </c>
-      <c r="B31" s="10">
+      <c r="B31" s="2">
         <v>46070</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>3</v>
       </c>
       <c r="U31" s="16" t="s">
         <v>74</v>
@@ -2371,7 +2402,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="32" ht="260" spans="1:32">
+    <row r="32" ht="260" spans="1:33">
       <c r="A32" s="8" t="s">
         <v>76</v>
       </c>
@@ -2426,16 +2457,16 @@
       <c r="F34" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="U34" s="28" t="s">
+      <c r="U34" s="25" t="s">
         <v>83</v>
       </c>
-      <c r="V34" t="s">
-        <v>84</v>
+      <c r="V34" s="1" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="35" ht="364" spans="1:26">
       <c r="A35" s="24" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B35" s="2">
         <v>46082</v>
@@ -2446,8 +2477,8 @@
       <c r="D35" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="U35" s="26" t="s">
-        <v>86</v>
+      <c r="U35" s="28" t="s">
+        <v>85</v>
       </c>
       <c r="Z35" s="10">
         <v>46141</v>
@@ -2455,21 +2486,21 @@
     </row>
     <row r="36" ht="26" spans="1:26">
       <c r="A36" s="16" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F36" s="10">
         <v>46082</v>
       </c>
       <c r="U36" s="29" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="Y36" s="10">
         <v>46147</v>
       </c>
     </row>
     <row r="37" ht="26" spans="1:26">
-      <c r="A37" s="26" t="s">
-        <v>89</v>
+      <c r="A37" s="28" t="s">
+        <v>88</v>
       </c>
       <c r="G37" s="10">
         <v>46084</v>
@@ -2478,7 +2509,7 @@
     </row>
     <row r="38" ht="26" spans="1:26">
       <c r="A38" s="8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
@@ -2493,8 +2524,8 @@
       </c>
     </row>
     <row r="39" ht="26" spans="1:26">
-      <c r="A39" s="30" t="s">
-        <v>91</v>
+      <c r="A39" s="26" t="s">
+        <v>90</v>
       </c>
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
@@ -2507,27 +2538,54 @@
       </c>
     </row>
     <row r="40" ht="26" spans="1:26">
-      <c r="A40" s="16" t="s">
+      <c r="A40" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B40" s="13"/>
+      <c r="C40" s="13"/>
+      <c r="D40" s="13"/>
+      <c r="E40" s="13"/>
+      <c r="F40" s="13"/>
+      <c r="G40" s="13"/>
+      <c r="H40" s="13"/>
+      <c r="I40" s="13" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="41" ht="26" spans="1:26">
+      <c r="A41" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="I40" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="41" ht="26" spans="1:26">
-      <c r="A41" s="16" t="s">
+      <c r="B41" s="13"/>
+      <c r="C41" s="13"/>
+      <c r="D41" s="13"/>
+      <c r="E41" s="13"/>
+      <c r="F41" s="13" t="s">
         <v>93</v>
-      </c>
-      <c r="F41" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="42" spans="1:26">
       <c r="A42" t="s">
+        <v>94</v>
+      </c>
+      <c r="D42" t="s">
         <v>95</v>
       </c>
-      <c r="D42" t="s">
+    </row>
+    <row r="43" ht="26" spans="1:26">
+      <c r="A43" s="16" t="s">
         <v>96</v>
+      </c>
+      <c r="F43" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="44" ht="26" spans="1:26">
+      <c r="A44" s="30" t="s">
+        <v>98</v>
+      </c>
+      <c r="E44" t="s">
+        <v>99</v>
       </c>
     </row>
   </sheetData>
@@ -2577,6 +2635,8 @@
     <hyperlink ref="A41" r:id="rId44" display="687. Longest Univalue Path" tooltip="https://leetcode.com/problems/longest-univalue-path/"/>
     <hyperlink ref="U34" r:id="rId45" display="692. Top K Frequent Words" tooltip="https://leetcode.com/problems/top-k-frequent-words/"/>
     <hyperlink ref="U35" r:id="rId46" display="678. Valid Parenthesis String" tooltip="https://leetcode.com/problems/valid-parenthesis-string/"/>
+    <hyperlink ref="A43" r:id="rId47" display="547. Number of Provinces" tooltip="https://leetcode.com/problems/number-of-provinces/"/>
+    <hyperlink ref="A44" r:id="rId48" display="994. Rotting Oranges" tooltip="https://leetcode.com/problems/rotting-oranges/"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/DSA_REV.xlsx
+++ b/DSA_REV.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18350" windowHeight="8000"/>
+    <workbookView windowWidth="18350" windowHeight="7400"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="102">
   <si>
     <t>problem</t>
   </si>
@@ -327,6 +327,12 @@
   </si>
   <si>
     <t>1545. Find Kth Bit in Nth Binary String</t>
+  </si>
+  <si>
+    <t>1838. Frequency of the Most Frequent Element</t>
+  </si>
+  <si>
+    <t>14may</t>
   </si>
   <si>
     <t>238. Product of Array Except Self</t>
@@ -1059,7 +1065,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1158,9 +1164,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2423,7 +2426,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="33" ht="26" spans="1:26">
+    <row r="33" ht="26" spans="1:29">
       <c r="A33" s="8" t="s">
         <v>79</v>
       </c>
@@ -2444,7 +2447,7 @@
         <v>46108</v>
       </c>
     </row>
-    <row r="34" ht="182" spans="1:26">
+    <row r="34" ht="182" spans="1:29">
       <c r="A34" s="8" t="s">
         <v>81</v>
       </c>
@@ -2464,7 +2467,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="35" ht="364" spans="1:26">
+    <row r="35" ht="364" spans="1:29">
       <c r="A35" s="24" t="s">
         <v>84</v>
       </c>
@@ -2484,7 +2487,7 @@
         <v>46141</v>
       </c>
     </row>
-    <row r="36" ht="26" spans="1:26">
+    <row r="36" ht="26" spans="1:29">
       <c r="A36" s="16" t="s">
         <v>86</v>
       </c>
@@ -2498,18 +2501,23 @@
         <v>46147</v>
       </c>
     </row>
-    <row r="37" ht="26" spans="1:26">
+    <row r="37" ht="26" spans="1:29">
       <c r="A37" s="28" t="s">
         <v>88</v>
       </c>
       <c r="G37" s="10">
         <v>46084</v>
       </c>
-      <c r="U37" s="29"/>
-    </row>
-    <row r="38" ht="26" spans="1:26">
+      <c r="U37" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="AC37" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="38" ht="26" spans="1:29">
       <c r="A38" s="8" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
@@ -2523,9 +2531,9 @@
         <v>3</v>
       </c>
     </row>
-    <row r="39" ht="26" spans="1:26">
+    <row r="39" ht="26" spans="1:29">
       <c r="A39" s="26" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
@@ -2537,9 +2545,9 @@
         <v>3</v>
       </c>
     </row>
-    <row r="40" ht="26" spans="1:26">
+    <row r="40" ht="26" spans="1:29">
       <c r="A40" s="4" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B40" s="13"/>
       <c r="C40" s="13"/>
@@ -2552,40 +2560,40 @@
         <v>78</v>
       </c>
     </row>
-    <row r="41" ht="26" spans="1:26">
+    <row r="41" ht="26" spans="1:29">
       <c r="A41" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B41" s="13"/>
       <c r="C41" s="13"/>
       <c r="D41" s="13"/>
       <c r="E41" s="13"/>
       <c r="F41" s="13" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="42" spans="1:26">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="42" spans="1:29">
       <c r="A42" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D42" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="43" ht="26" spans="1:26">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="43" ht="26" spans="1:29">
       <c r="A43" s="16" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="F43" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="44" ht="26" spans="1:26">
-      <c r="A44" s="30" t="s">
-        <v>98</v>
+        <v>99</v>
+      </c>
+    </row>
+    <row r="44" ht="26" spans="1:29">
+      <c r="A44" s="28" t="s">
+        <v>100</v>
       </c>
       <c r="E44" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>
@@ -2637,6 +2645,7 @@
     <hyperlink ref="U35" r:id="rId46" display="678. Valid Parenthesis String" tooltip="https://leetcode.com/problems/valid-parenthesis-string/"/>
     <hyperlink ref="A43" r:id="rId47" display="547. Number of Provinces" tooltip="https://leetcode.com/problems/number-of-provinces/"/>
     <hyperlink ref="A44" r:id="rId48" display="994. Rotting Oranges" tooltip="https://leetcode.com/problems/rotting-oranges/"/>
+    <hyperlink ref="U37" r:id="rId49" display="1838. Frequency of the Most Frequent Element" tooltip="https://leetcode.com/problems/frequency-of-the-most-frequent-element/"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/DSA_REV.xlsx
+++ b/DSA_REV.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="106">
   <si>
     <t>problem</t>
   </si>
@@ -366,6 +366,18 @@
   </si>
   <si>
     <t>11may</t>
+  </si>
+  <si>
+    <t>802. Find Eventual Safe States</t>
+  </si>
+  <si>
+    <t>20may</t>
+  </si>
+  <si>
+    <t>542. 01 Matrix</t>
+  </si>
+  <si>
+    <t>21may</t>
   </si>
 </sst>
 </file>
@@ -1065,7 +1077,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1164,6 +1176,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1699,7 +1714,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AG44"/>
+  <dimension ref="A1:AG46"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="8.81818181818182"/>
@@ -2233,11 +2248,14 @@
       </c>
     </row>
     <row r="24" ht="208" spans="1:33">
-      <c r="A24" s="9" t="s">
+      <c r="A24" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="B24" s="10">
+      <c r="B24" s="2">
         <v>46054</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>3</v>
       </c>
       <c r="U24" s="25" t="s">
         <v>56</v>
@@ -2250,11 +2268,14 @@
       </c>
     </row>
     <row r="25" ht="156" spans="1:33">
-      <c r="A25" s="9" t="s">
+      <c r="A25" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="B25" s="10">
+      <c r="B25" s="21">
         <v>46054</v>
+      </c>
+      <c r="C25" s="13" t="s">
+        <v>6</v>
       </c>
       <c r="U25" s="8" t="s">
         <v>58</v>
@@ -2327,12 +2348,19 @@
       <c r="C28" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="U28" t="s">
+      <c r="U28" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="W28" s="10">
+      <c r="V28" s="1"/>
+      <c r="W28" s="2">
         <v>46083</v>
       </c>
+      <c r="X28" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y28" s="1"/>
+      <c r="Z28" s="1"/>
+      <c r="AA28" s="1"/>
     </row>
     <row r="29" ht="26" spans="1:33">
       <c r="A29" s="16" t="s">
@@ -2398,11 +2426,18 @@
       <c r="C31" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="U31" s="16" t="s">
+      <c r="U31" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="Z31" t="s">
+      <c r="V31" s="1"/>
+      <c r="W31" s="1"/>
+      <c r="X31" s="1"/>
+      <c r="Y31" s="1"/>
+      <c r="Z31" s="1" t="s">
         <v>75</v>
+      </c>
+      <c r="AA31" s="1" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="32" ht="260" spans="1:33">
@@ -2594,6 +2629,22 @@
       </c>
       <c r="E44" t="s">
         <v>101</v>
+      </c>
+    </row>
+    <row r="45" ht="26" spans="1:29">
+      <c r="A45" s="16" t="s">
+        <v>102</v>
+      </c>
+      <c r="F45" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="46" ht="26" spans="1:29">
+      <c r="A46" s="30" t="s">
+        <v>104</v>
+      </c>
+      <c r="D46" t="s">
+        <v>105</v>
       </c>
     </row>
   </sheetData>
@@ -2646,6 +2697,8 @@
     <hyperlink ref="A43" r:id="rId47" display="547. Number of Provinces" tooltip="https://leetcode.com/problems/number-of-provinces/"/>
     <hyperlink ref="A44" r:id="rId48" display="994. Rotting Oranges" tooltip="https://leetcode.com/problems/rotting-oranges/"/>
     <hyperlink ref="U37" r:id="rId49" display="1838. Frequency of the Most Frequent Element" tooltip="https://leetcode.com/problems/frequency-of-the-most-frequent-element/"/>
+    <hyperlink ref="A45" r:id="rId50" display="802. Find Eventual Safe States" tooltip="https://leetcode.com/problems/find-eventual-safe-states/"/>
+    <hyperlink ref="A46" r:id="rId51" display="542. 01 Matrix" tooltip="https://leetcode.com/problems/01-matrix/"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/DSA_REV.xlsx
+++ b/DSA_REV.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18350" windowHeight="7400"/>
+    <workbookView windowWidth="18350" windowHeight="8000"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="108">
   <si>
     <t>problem</t>
   </si>
@@ -378,6 +378,12 @@
   </si>
   <si>
     <t>21may</t>
+  </si>
+  <si>
+    <t>1631. Path With Minimum Effort</t>
+  </si>
+  <si>
+    <t>25may</t>
   </si>
 </sst>
 </file>
@@ -598,12 +604,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="Times New Roman"/>
       <charset val="0"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="Times New Roman"/>
       <charset val="0"/>
@@ -1178,8 +1184,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1714,7 +1720,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AG46"/>
+  <dimension ref="A1:AG47"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="8.81818181818182"/>
@@ -2640,11 +2646,19 @@
       </c>
     </row>
     <row r="46" ht="26" spans="1:29">
-      <c r="A46" s="30" t="s">
+      <c r="A46" s="16" t="s">
         <v>104</v>
       </c>
       <c r="D46" t="s">
         <v>105</v>
+      </c>
+    </row>
+    <row r="47" ht="156" spans="1:29">
+      <c r="A47" s="30" t="s">
+        <v>106</v>
+      </c>
+      <c r="B47" t="s">
+        <v>107</v>
       </c>
     </row>
   </sheetData>
@@ -2699,6 +2713,7 @@
     <hyperlink ref="U37" r:id="rId49" display="1838. Frequency of the Most Frequent Element" tooltip="https://leetcode.com/problems/frequency-of-the-most-frequent-element/"/>
     <hyperlink ref="A45" r:id="rId50" display="802. Find Eventual Safe States" tooltip="https://leetcode.com/problems/find-eventual-safe-states/"/>
     <hyperlink ref="A46" r:id="rId51" display="542. 01 Matrix" tooltip="https://leetcode.com/problems/01-matrix/"/>
+    <hyperlink ref="A47" r:id="rId52" display="1631. Path With Minimum Effort" tooltip="https://leetcode.com/problems/path-with-minimum-effort/"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/DSA_REV.xlsx
+++ b/DSA_REV.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18350" windowHeight="8000"/>
+    <workbookView windowWidth="18350" windowHeight="7400"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="110">
   <si>
     <t>problem</t>
   </si>
@@ -384,6 +384,12 @@
   </si>
   <si>
     <t>25may</t>
+  </si>
+  <si>
+    <t>787. Cheapest Flights Within K Stops</t>
+  </si>
+  <si>
+    <t>26may</t>
   </si>
 </sst>
 </file>
@@ -604,12 +610,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="Times New Roman"/>
       <charset val="0"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="Times New Roman"/>
       <charset val="0"/>
@@ -1184,8 +1190,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1720,7 +1726,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AG47"/>
+  <dimension ref="A1:AG48"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="8.81818181818182"/>
@@ -2654,11 +2660,19 @@
       </c>
     </row>
     <row r="47" ht="156" spans="1:29">
-      <c r="A47" s="30" t="s">
+      <c r="A47" s="27" t="s">
         <v>106</v>
       </c>
       <c r="B47" t="s">
         <v>107</v>
+      </c>
+    </row>
+    <row r="48" ht="26" spans="1:29">
+      <c r="A48" s="30" t="s">
+        <v>108</v>
+      </c>
+      <c r="G48" t="s">
+        <v>109</v>
       </c>
     </row>
   </sheetData>
@@ -2714,6 +2728,7 @@
     <hyperlink ref="A45" r:id="rId50" display="802. Find Eventual Safe States" tooltip="https://leetcode.com/problems/find-eventual-safe-states/"/>
     <hyperlink ref="A46" r:id="rId51" display="542. 01 Matrix" tooltip="https://leetcode.com/problems/01-matrix/"/>
     <hyperlink ref="A47" r:id="rId52" display="1631. Path With Minimum Effort" tooltip="https://leetcode.com/problems/path-with-minimum-effort/"/>
+    <hyperlink ref="A48" r:id="rId53" display="787. Cheapest Flights Within K Stops" tooltip="https://leetcode.com/problems/cheapest-flights-within-k-stops/"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/DSA_REV.xlsx
+++ b/DSA_REV.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18350" windowHeight="7400"/>
+    <workbookView windowWidth="18350" windowHeight="8000"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="115">
   <si>
     <t>problem</t>
   </si>
@@ -390,6 +390,21 @@
   </si>
   <si>
     <t>26may</t>
+  </si>
+  <si>
+    <t>3937. Minimum Operations to Make Array Modulo Alternating I</t>
+  </si>
+  <si>
+    <t>27may</t>
+  </si>
+  <si>
+    <t>41. First Missing Positive</t>
+  </si>
+  <si>
+    <t>2june</t>
+  </si>
+  <si>
+    <t>3942. Minimum Operations to Sort a Permutation</t>
   </si>
 </sst>
 </file>
@@ -1089,7 +1104,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1181,17 +1196,23 @@
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1726,7 +1747,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AG48"/>
+  <dimension ref="A1:AG51"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="8.81818181818182"/>
@@ -2466,11 +2487,14 @@
       <c r="G32" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="U32" s="27" t="s">
+      <c r="U32" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="V32" t="s">
+      <c r="V32" s="1" t="s">
         <v>78</v>
+      </c>
+      <c r="W32" s="1" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="33" ht="26" spans="1:29">
@@ -2487,11 +2511,16 @@
       <c r="G33" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="U33" s="16" t="s">
+      <c r="U33" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="X33" s="10">
+      <c r="V33" s="1"/>
+      <c r="W33" s="1"/>
+      <c r="X33" s="2">
         <v>46108</v>
+      </c>
+      <c r="Y33" s="1" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="34" ht="182" spans="1:29">
@@ -2527,11 +2556,18 @@
       <c r="D35" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="U35" s="28" t="s">
+      <c r="U35" s="27" t="s">
         <v>85</v>
       </c>
-      <c r="Z35" s="10">
+      <c r="V35" s="20"/>
+      <c r="W35" s="20"/>
+      <c r="X35" s="20"/>
+      <c r="Y35" s="20"/>
+      <c r="Z35" s="28">
         <v>46141</v>
+      </c>
+      <c r="AA35" s="20" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="36" ht="26" spans="1:29">
@@ -2544,12 +2580,18 @@
       <c r="U36" s="29" t="s">
         <v>87</v>
       </c>
-      <c r="Y36" s="10">
+      <c r="V36" s="1"/>
+      <c r="W36" s="1"/>
+      <c r="X36" s="1"/>
+      <c r="Y36" s="2">
         <v>46147</v>
       </c>
+      <c r="Z36" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="37" ht="26" spans="1:29">
-      <c r="A37" s="28" t="s">
+      <c r="A37" s="30" t="s">
         <v>88</v>
       </c>
       <c r="G37" s="10">
@@ -2608,15 +2650,18 @@
       </c>
     </row>
     <row r="41" ht="26" spans="1:29">
-      <c r="A41" s="4" t="s">
+      <c r="A41" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="B41" s="13"/>
-      <c r="C41" s="13"/>
-      <c r="D41" s="13"/>
-      <c r="E41" s="13"/>
+      <c r="B41" s="1"/>
+      <c r="C41" s="1"/>
+      <c r="D41" s="1"/>
+      <c r="E41" s="1"/>
       <c r="F41" s="13" t="s">
         <v>95</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="42" spans="1:29">
@@ -2636,7 +2681,7 @@
       </c>
     </row>
     <row r="44" ht="26" spans="1:29">
-      <c r="A44" s="28" t="s">
+      <c r="A44" s="30" t="s">
         <v>100</v>
       </c>
       <c r="E44" t="s">
@@ -2660,7 +2705,7 @@
       </c>
     </row>
     <row r="47" ht="156" spans="1:29">
-      <c r="A47" s="27" t="s">
+      <c r="A47" s="31" t="s">
         <v>106</v>
       </c>
       <c r="B47" t="s">
@@ -2668,11 +2713,35 @@
       </c>
     </row>
     <row r="48" ht="26" spans="1:29">
-      <c r="A48" s="30" t="s">
+      <c r="A48" s="16" t="s">
         <v>108</v>
       </c>
       <c r="G48" t="s">
         <v>109</v>
+      </c>
+    </row>
+    <row r="49" ht="364" spans="1:9">
+      <c r="A49" s="32" t="s">
+        <v>110</v>
+      </c>
+      <c r="B49" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="50" ht="26" spans="1:9">
+      <c r="A50" s="16" t="s">
+        <v>112</v>
+      </c>
+      <c r="E50" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="51" ht="26" spans="1:9">
+      <c r="A51" s="16" t="s">
+        <v>114</v>
+      </c>
+      <c r="I51" t="s">
+        <v>113</v>
       </c>
     </row>
   </sheetData>
@@ -2729,6 +2798,9 @@
     <hyperlink ref="A46" r:id="rId51" display="542. 01 Matrix" tooltip="https://leetcode.com/problems/01-matrix/"/>
     <hyperlink ref="A47" r:id="rId52" display="1631. Path With Minimum Effort" tooltip="https://leetcode.com/problems/path-with-minimum-effort/"/>
     <hyperlink ref="A48" r:id="rId53" display="787. Cheapest Flights Within K Stops" tooltip="https://leetcode.com/problems/cheapest-flights-within-k-stops/"/>
+    <hyperlink ref="A49" r:id="rId54" display="3937. Minimum Operations to Make Array Modulo Alternating I" tooltip="https://leetcode.com/problems/minimum-operations-to-make-array-modulo-alternating-i/"/>
+    <hyperlink ref="A50" r:id="rId55" display="41. First Missing Positive" tooltip="https://leetcode.com/problems/first-missing-positive/"/>
+    <hyperlink ref="A51" r:id="rId56" display="3942. Minimum Operations to Sort a Permutation" tooltip="https://leetcode.com/problems/minimum-operations-to-sort-a-permutation/"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/DSA_REV.xlsx
+++ b/DSA_REV.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18350" windowHeight="8000"/>
+    <workbookView windowWidth="18350" windowHeight="7400"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="118">
   <si>
     <t>problem</t>
   </si>
@@ -405,6 +405,15 @@
   </si>
   <si>
     <t>3942. Minimum Operations to Sort a Permutation</t>
+  </si>
+  <si>
+    <t>947. Most Stones Removed with Same Row or Column</t>
+  </si>
+  <si>
+    <t>4june</t>
+  </si>
+  <si>
+    <t>2598. Smallest Missing Non-negative Integer After Operations</t>
   </si>
 </sst>
 </file>
@@ -1747,7 +1756,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AG51"/>
+  <dimension ref="A1:AG53"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="8.81818181818182"/>
@@ -2720,7 +2729,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="49" ht="364" spans="1:9">
+    <row r="49" ht="364" spans="1:11">
       <c r="A49" s="32" t="s">
         <v>110</v>
       </c>
@@ -2728,7 +2737,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="50" ht="26" spans="1:9">
+    <row r="50" ht="26" spans="1:11">
       <c r="A50" s="16" t="s">
         <v>112</v>
       </c>
@@ -2736,12 +2745,28 @@
         <v>113</v>
       </c>
     </row>
-    <row r="51" ht="26" spans="1:9">
+    <row r="51" ht="26" spans="1:11">
       <c r="A51" s="16" t="s">
         <v>114</v>
       </c>
       <c r="I51" t="s">
         <v>113</v>
+      </c>
+    </row>
+    <row r="52" ht="26" spans="1:11">
+      <c r="A52" s="16" t="s">
+        <v>115</v>
+      </c>
+      <c r="J52" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="53" ht="26" spans="1:11">
+      <c r="A53" s="16" t="s">
+        <v>117</v>
+      </c>
+      <c r="K53" t="s">
+        <v>116</v>
       </c>
     </row>
   </sheetData>
@@ -2801,6 +2826,8 @@
     <hyperlink ref="A49" r:id="rId54" display="3937. Minimum Operations to Make Array Modulo Alternating I" tooltip="https://leetcode.com/problems/minimum-operations-to-make-array-modulo-alternating-i/"/>
     <hyperlink ref="A50" r:id="rId55" display="41. First Missing Positive" tooltip="https://leetcode.com/problems/first-missing-positive/"/>
     <hyperlink ref="A51" r:id="rId56" display="3942. Minimum Operations to Sort a Permutation" tooltip="https://leetcode.com/problems/minimum-operations-to-sort-a-permutation/"/>
+    <hyperlink ref="A52" r:id="rId57" display="947. Most Stones Removed with Same Row or Column" tooltip="https://leetcode.com/problems/most-stones-removed-with-same-row-or-column/"/>
+    <hyperlink ref="A53" r:id="rId58" display="2598. Smallest Missing Non-negative Integer After Operations" tooltip="https://leetcode.com/problems/smallest-missing-non-negative-integer-after-operations/"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
